--- a/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,75</t>
+          <t>7,96; 17,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,91; 15,97</t>
+          <t>6,97; 16,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 10,63</t>
+          <t>2,92; 10,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 17,54</t>
+          <t>7,9; 17,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,03</t>
+          <t>6,13; 13,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 16,44</t>
+          <t>7,47; 16,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,72</t>
+          <t>5,23; 12,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 20,32</t>
+          <t>8,74; 20,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,05</t>
+          <t>7,74; 13,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,3</t>
+          <t>8,36; 14,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,09</t>
+          <t>4,77; 10,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 17,01</t>
+          <t>9,39; 17,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,35; 18,02</t>
+          <t>10,75; 18,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,9</t>
+          <t>5,47; 11,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,13</t>
+          <t>5,7; 11,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,15</t>
+          <t>8,09; 15,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,61</t>
+          <t>7,3; 14,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,8; 16,03</t>
+          <t>8,56; 15,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 11,91</t>
+          <t>6,03; 12,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 17,13</t>
+          <t>9,37; 17,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,93</t>
+          <t>9,79; 14,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,77</t>
+          <t>8,02; 12,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,8</t>
+          <t>6,44; 10,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 15,25</t>
+          <t>9,84; 15,41</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 12,72</t>
+          <t>5,21; 13,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 11,73</t>
+          <t>4,97; 12,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 16,54</t>
+          <t>8,22; 16,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,31</t>
+          <t>3,11; 9,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,85</t>
+          <t>7,21; 15,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 13,41</t>
+          <t>6,19; 13,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,93</t>
+          <t>6,46; 14,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,76</t>
+          <t>3,11; 9,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 12,6</t>
+          <t>7,35; 12,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,33</t>
+          <t>6,45; 11,11</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,03</t>
+          <t>8,48; 13,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 8,19</t>
+          <t>3,78; 8,16</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,94; 15,52</t>
+          <t>8,02; 15,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 18,63</t>
+          <t>10,07; 18,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,32</t>
+          <t>7,54; 15,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,84</t>
+          <t>4,36; 11,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 11,17</t>
+          <t>5,03; 11,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,64; 14,56</t>
+          <t>7,83; 15,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 13,59</t>
+          <t>6,94; 14,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,93</t>
+          <t>7,4; 15,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,04</t>
+          <t>7,35; 12,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,48</t>
+          <t>10,03; 15,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 13,22</t>
+          <t>8,03; 13,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 12,2</t>
+          <t>6,58; 12,17</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,84</t>
+          <t>9,61; 13,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,34</t>
+          <t>8,8; 12,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,28</t>
+          <t>7,62; 11,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,95</t>
+          <t>7,18; 11,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,22</t>
+          <t>7,83; 11,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,99</t>
+          <t>9,13; 12,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,15</t>
+          <t>7,65; 11,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,95</t>
+          <t>8,86; 12,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 11,82</t>
+          <t>9,07; 11,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,41; 12,07</t>
+          <t>9,28; 12,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,68</t>
+          <t>8,15; 10,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,56</t>
+          <t>8,72; 11,66</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>16361</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7924</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14307</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>17602</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>19073</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>30581</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32773</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>20116</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>33380</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>10981; 23875</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9623; 22128</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3858; 13650</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9264; 20848</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9206; 20740</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11515; 25246</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7743; 18858</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>12273; 28348</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>22298; 38796</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>24424; 43267</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13375; 28209</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>24209; 45047</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>27548</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16797</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16949</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22124</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>21401</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26361</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19063</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>32888</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>48949</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>43158</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36012</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>55012</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>20919; 36175</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>11183; 23297</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11638; 24257</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15407; 30404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>15337; 30067</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>18926; 34046</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>13407; 27035</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23892; 44451</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>39631; 60120</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>34119; 53774</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>27468; 46422</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>43836; 68675</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>11693</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11995</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18274</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11288</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15886</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>15135</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>16826</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10567</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>27580</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27129</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35101</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>21855</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7185; 17957</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7649; 18797</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12692; 25762</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>5894; 18668</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10751; 23171</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10141; 22002</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10723; 24250</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5749; 17287</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>21086; 36232</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20490; 35275</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27163; 44465</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14171; 30548</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>23305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29256</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22391</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>16093</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20572</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20268</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>39398</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51441</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>42963</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>32268</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>16736; 32369</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20867; 39155</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15531; 31278</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7265; 18427</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10410; 23608</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16140; 31240</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>14025; 28888</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>13404; 28750</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>30545; 51459</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>41464; 63972</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>32779; 54291</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>22910; 42366</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>78908</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>65539</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>59719</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>146507</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>154501</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>134191</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>142515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>65248; 92607</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>61927; 87534</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53124; 78190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>47668; 74045</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>56136; 80860</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>67988; 96061</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>56504; 83849</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>67496; 98738</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>126605; 165722</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>134359; 174051</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>116934; 152569</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>124334; 166277</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,96; 17,3</t>
+          <t>8,11; 17,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 16,03</t>
+          <t>7,2; 15,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 10,31</t>
+          <t>2,99; 10,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 17,78</t>
+          <t>7,73; 17,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 13,8</t>
+          <t>6,31; 13,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 16,39</t>
+          <t>7,84; 15,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 12,74</t>
+          <t>4,83; 12,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 20,19</t>
+          <t>8,33; 20,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,74; 13,46</t>
+          <t>7,94; 13,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 14,81</t>
+          <t>8,3; 14,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 10,06</t>
+          <t>4,98; 9,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,48</t>
+          <t>9,44; 17,5</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 18,6</t>
+          <t>10,72; 18,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,39</t>
+          <t>5,52; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,88</t>
+          <t>5,57; 12,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,09; 15,96</t>
+          <t>8,16; 16,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 14,31</t>
+          <t>7,15; 13,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 15,4</t>
+          <t>8,58; 15,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,15</t>
+          <t>5,97; 12,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 17,43</t>
+          <t>9,13; 17,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,86</t>
+          <t>9,75; 14,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,63</t>
+          <t>7,96; 12,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,88</t>
+          <t>6,58; 10,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,84; 15,41</t>
+          <t>10,14; 15,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,03</t>
+          <t>5,34; 13,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,22</t>
+          <t>4,75; 11,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 16,69</t>
+          <t>8,31; 16,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,85</t>
+          <t>3,25; 9,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 15,55</t>
+          <t>6,92; 14,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 13,44</t>
+          <t>6,37; 13,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,61</t>
+          <t>6,96; 14,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,35</t>
+          <t>3,09; 9,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,63</t>
+          <t>6,94; 12,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,11</t>
+          <t>6,38; 11,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 13,88</t>
+          <t>8,44; 13,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,16</t>
+          <t>3,74; 8,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 15,51</t>
+          <t>7,93; 15,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,07; 18,9</t>
+          <t>10,11; 18,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 15,18</t>
+          <t>7,36; 14,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,05</t>
+          <t>4,48; 11,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,4</t>
+          <t>5,16; 10,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,16</t>
+          <t>7,46; 14,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,3</t>
+          <t>7,13; 14,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 15,86</t>
+          <t>7,53; 15,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 12,38</t>
+          <t>7,24; 11,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,48</t>
+          <t>9,97; 15,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 13,3</t>
+          <t>8,08; 13,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,17</t>
+          <t>6,76; 12,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,64</t>
+          <t>9,67; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,44</t>
+          <t>8,77; 12,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,62; 11,22</t>
+          <t>7,7; 11,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,15</t>
+          <t>7,17; 11,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,28</t>
+          <t>7,73; 11,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 12,89</t>
+          <t>9,14; 12,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,35</t>
+          <t>7,51; 11,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 12,97</t>
+          <t>8,8; 13,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,87</t>
+          <t>9,09; 11,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,02</t>
+          <t>9,36; 12,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 10,63</t>
+          <t>8,16; 10,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 11,66</t>
+          <t>8,67; 11,63</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año (tasa de respuesta: 99,31%)</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10981; 23875</t>
+          <t>11196; 23716</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9623; 22128</t>
+          <t>9933; 21843</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3858; 13650</t>
+          <t>3963; 13581</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9264; 20848</t>
+          <t>9065; 20574</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9206; 20740</t>
+          <t>9479; 21009</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11515; 25246</t>
+          <t>12075; 24357</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7743; 18858</t>
+          <t>7151; 18906</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12273; 28348</t>
+          <t>11703; 28862</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22298; 38796</t>
+          <t>22883; 39076</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24424; 43267</t>
+          <t>24255; 42934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13375; 28209</t>
+          <t>13965; 28001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24209; 45047</t>
+          <t>24321; 45098</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20919; 36175</t>
+          <t>20859; 35585</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11183; 23297</t>
+          <t>11280; 23884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11638; 24257</t>
+          <t>11371; 24716</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15407; 30404</t>
+          <t>15551; 30728</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15337; 30067</t>
+          <t>15035; 28950</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18926; 34046</t>
+          <t>18980; 35170</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13407; 27035</t>
+          <t>13271; 26772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23892; 44451</t>
+          <t>23278; 43582</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39631; 60120</t>
+          <t>39465; 59530</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34119; 53774</t>
+          <t>33863; 54014</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27468; 46422</t>
+          <t>28057; 46594</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43836; 68675</t>
+          <t>45199; 67831</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7185; 17957</t>
+          <t>7366; 17942</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7649; 18797</t>
+          <t>7301; 18105</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12692; 25762</t>
+          <t>12819; 24718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5894; 18668</t>
+          <t>6167; 18238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10751; 23171</t>
+          <t>10308; 22296</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10141; 22002</t>
+          <t>10423; 22460</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10723; 24250</t>
+          <t>11549; 23869</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5749; 17287</t>
+          <t>5719; 18060</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21086; 36232</t>
+          <t>19905; 35744</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20490; 35275</t>
+          <t>20271; 35915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27163; 44465</t>
+          <t>27049; 44803</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14171; 30548</t>
+          <t>14000; 31365</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16736; 32369</t>
+          <t>16537; 32513</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20867; 39155</t>
+          <t>20954; 38345</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15531; 31278</t>
+          <t>15172; 30356</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7265; 18427</t>
+          <t>7479; 18401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10410; 23608</t>
+          <t>10696; 22647</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16140; 31240</t>
+          <t>15375; 29991</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14025; 28888</t>
+          <t>14414; 28361</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13404; 28750</t>
+          <t>13647; 28587</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30545; 51459</t>
+          <t>30104; 49761</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41464; 63972</t>
+          <t>41186; 63759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32779; 54291</t>
+          <t>32971; 54029</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22910; 42366</t>
+          <t>23530; 42865</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65248; 92607</t>
+          <t>65682; 92845</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61927; 87534</t>
+          <t>61693; 87705</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53124; 78190</t>
+          <t>53642; 78767</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47668; 74045</t>
+          <t>47650; 73478</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>56136; 80860</t>
+          <t>55401; 82080</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67988; 96061</t>
+          <t>68057; 96554</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>56504; 83849</t>
+          <t>55483; 82556</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67496; 98738</t>
+          <t>67044; 99187</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126605; 165722</t>
+          <t>126903; 164698</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134359; 174051</t>
+          <t>135645; 174286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>116934; 152569</t>
+          <t>117201; 152216</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>124334; 166277</t>
+          <t>123542; 165872</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP26C_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,43%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15,07%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>11,85%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,99%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 17,18</t>
+          <t>5,95; 14,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 15,82</t>
+          <t>7,82; 16,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,26</t>
+          <t>4,81; 12,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,54</t>
+          <t>9,68; 22,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,98</t>
+          <t>8,34; 16,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,81</t>
+          <t>6,91; 15,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 12,77</t>
+          <t>3,2; 10,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 20,56</t>
+          <t>7,68; 16,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,56</t>
+          <t>8,1; 14,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 14,7</t>
+          <t>8,3; 14,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,99</t>
+          <t>4,96; 10,09</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 17,5</t>
+          <t>9,68; 17,67</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>8,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,29</t>
+          <t>7,16; 13,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,68</t>
+          <t>8,8; 16,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,1</t>
+          <t>5,95; 11,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,16; 16,13</t>
+          <t>9,25; 17,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,78</t>
+          <t>10,35; 18,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,9</t>
+          <t>5,52; 11,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,03</t>
+          <t>5,76; 12,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,09</t>
+          <t>8,71; 16,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 14,71</t>
+          <t>9,75; 14,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,69</t>
+          <t>8,07; 12,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,92</t>
+          <t>6,59; 10,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,22</t>
+          <t>10,15; 15,53</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,24%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10,14%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,48%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 13,02</t>
+          <t>7,15; 14,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 11,77</t>
+          <t>6,22; 13,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 16,02</t>
+          <t>6,94; 14,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,62</t>
+          <t>3,29; 10,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 14,96</t>
+          <t>5,41; 12,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,72</t>
+          <t>4,92; 11,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,38</t>
+          <t>8,31; 16,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,77</t>
+          <t>4,26; 11,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,46</t>
+          <t>7,12; 12,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,31</t>
+          <t>6,3; 11,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,44; 13,99</t>
+          <t>8,44; 14,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,38</t>
+          <t>4,68; 9,55</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,87%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,58</t>
+          <t>5,07; 11,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 18,51</t>
+          <t>7,64; 14,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 14,73</t>
+          <t>7,09; 13,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,03</t>
+          <t>7,54; 16,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 10,93</t>
+          <t>7,94; 15,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 14,56</t>
+          <t>10,2; 18,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,04</t>
+          <t>7,65; 15,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 15,77</t>
+          <t>4,56; 11,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,24; 11,97</t>
+          <t>7,16; 12,04</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 15,43</t>
+          <t>9,78; 15,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 13,24</t>
+          <t>7,93; 13,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 12,32</t>
+          <t>6,86; 12,54</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>11,62%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,41%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,4%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,91%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 13,67</t>
+          <t>7,78; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 12,47</t>
+          <t>9,18; 12,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,7; 11,3</t>
+          <t>7,64; 11,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,06</t>
+          <t>9,13; 13,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,45</t>
+          <t>9,7; 13,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 12,96</t>
+          <t>8,56; 12,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51; 11,18</t>
+          <t>7,59; 11,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,8; 13,02</t>
+          <t>7,78; 11,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 11,8</t>
+          <t>9,31; 11,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,03</t>
+          <t>9,41; 12,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,6</t>
+          <t>8,16; 10,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,63</t>
+          <t>9,2; 12,14</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,37 +1509,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17602</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12191</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18977</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>16361</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>7924</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14220</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17602</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12191</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33380</t>
+          <t>33206</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11196; 23716</t>
+          <t>8936; 21080</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9933; 21843</t>
+          <t>12041; 25327</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3963; 13581</t>
+          <t>7119; 18829</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9065; 20574</t>
+          <t>12184; 28494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9479; 21009</t>
+          <t>11507; 23114</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12075; 24357</t>
+          <t>9541; 22043</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7151; 18906</t>
+          <t>4233; 14064</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11703; 28862</t>
+          <t>9304; 20554</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22883; 39076</t>
+          <t>23363; 40507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24255; 42934</t>
+          <t>24243; 41769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13965; 28001</t>
+          <t>13923; 28289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24321; 45098</t>
+          <t>23897; 43653</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21401</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26361</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19063</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>30382</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27548</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16797</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16949</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22124</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21401</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26361</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>19063</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32888</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55012</t>
+          <t>52937</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20859; 35585</t>
+          <t>15048; 28604</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11280; 23884</t>
+          <t>19464; 35447</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11371; 24716</t>
+          <t>13231; 26488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15551; 30728</t>
+          <t>21936; 40516</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15035; 28950</t>
+          <t>20126; 35057</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18980; 35170</t>
+          <t>11298; 24343</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13271; 26772</t>
+          <t>11763; 24770</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23278; 43582</t>
+          <t>16056; 31196</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39465; 59530</t>
+          <t>39444; 60427</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33863; 54014</t>
+          <t>34356; 54363</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28057; 46594</t>
+          <t>28101; 46095</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45199; 67831</t>
+          <t>42801; 65461</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>15886</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15135</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16826</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11693</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>11995</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>18274</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11288</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>15886</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15135</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>16826</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>11328</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21800</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7366; 17942</t>
+          <t>10654; 22124</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7301; 18105</t>
+          <t>10186; 21956</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12819; 24718</t>
+          <t>11527; 24774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6167; 18238</t>
+          <t>5534; 17873</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10308; 22296</t>
+          <t>7449; 17531</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10423; 22460</t>
+          <t>7573; 18045</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11549; 23869</t>
+          <t>12832; 25522</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5719; 18060</t>
+          <t>6657; 17547</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19905; 35744</t>
+          <t>20414; 36150</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20271; 35915</t>
+          <t>19993; 35974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27049; 44803</t>
+          <t>27020; 44933</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14000; 31365</t>
+          <t>15163; 30967</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>16093</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22185</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20572</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19284</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>23305</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>29256</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22391</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16093</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22185</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>20572</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>12664</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>31948</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16537; 32513</t>
+          <t>10509; 23135</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20954; 38345</t>
+          <t>15738; 30007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15172; 30356</t>
+          <t>14326; 27459</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7479; 18401</t>
+          <t>12763; 27793</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10696; 22647</t>
+          <t>16566; 32383</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15375; 29991</t>
+          <t>21135; 38593</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14414; 28361</t>
+          <t>15770; 31567</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13647; 28587</t>
+          <t>7564; 18842</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30104; 49761</t>
+          <t>29790; 50041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41186; 63759</t>
+          <t>40425; 63966</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32971; 54029</t>
+          <t>32351; 53964</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23530; 42865</t>
+          <t>23018; 42048</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>67600</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>81283</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68652</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>79116</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>73218</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>65539</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>59719</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>67600</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81283</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68652</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>60776</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139892</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65682; 92845</t>
+          <t>55776; 80366</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61693; 87705</t>
+          <t>68407; 96745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53642; 78767</t>
+          <t>56425; 82320</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47650; 73478</t>
+          <t>63956; 94496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>55401; 82080</t>
+          <t>65895; 93971</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>68057; 96554</t>
+          <t>60202; 86826</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55483; 82556</t>
+          <t>52926; 78613</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67044; 99187</t>
+          <t>48839; 73096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>126903; 164698</t>
+          <t>129891; 164954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>135645; 174286</t>
+          <t>136374; 174848</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>117201; 152216</t>
+          <t>117083; 153372</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>123542; 165872</t>
+          <t>122247; 161261</t>
         </is>
       </c>
     </row>
